--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2081,64 +2081,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359539</v>
+        <v>136532340</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>43280</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>101248</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stor-Kalvsberget Norra, Jmt</t>
+          <t>Z751 Lit, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488192</v>
+        <v>488469</v>
       </c>
       <c r="R14" t="n">
-        <v>7036152</v>
+        <v>7036130</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,17 +2146,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 födosökande talltita i lämplig häckbiotop.</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,36 +2162,35 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131359539</t>
+          <t>https://artportalen.se/Sighting/136532340</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>90569298</v>
+        <v>131359539</v>
       </c>
       <c r="B15" t="n">
-        <v>109815</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,34 +2198,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220204</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Husås – Andviken – väg Z751, Jmt</t>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488364</v>
+        <v>488192</v>
       </c>
       <c r="R15" t="n">
-        <v>7036217</v>
+        <v>7036152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,17 +2268,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Allmän</t>
+          <t>1 födosökande talltita i lämplig häckbiotop.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,84 +2290,73 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Therese Kalling</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90569298</t>
+          <t>https://artportalen.se/Sighting/131359539</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131359540</v>
+        <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>79350</v>
+        <v>108105</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>260591</v>
+        <v>219933</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Kalvsberget Norra, Jmt</t>
+          <t>Z751 Lit, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488103</v>
+        <v>488420</v>
       </c>
       <c r="R16" t="n">
-        <v>7036077</v>
+        <v>7036252</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2397,17 +2380,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,43 +2394,489 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537122</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136537147</v>
+      </c>
+      <c r="B17" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>488428</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7036229</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537147</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136537162</v>
+      </c>
+      <c r="B18" t="n">
+        <v>108105</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Z751 Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>488440</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7036213</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537162</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>90569298</v>
+      </c>
+      <c r="B19" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Husås – Andviken – väg Z751, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>488364</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7036217</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-07-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-07-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Allmän</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emma Karlsson, Therese Kalling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90569298</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131359540</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>488103</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7036077</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131359540</t>
         </is>
@@ -2475,6 +2899,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2084,7 +2084,7 @@
         <v>136532340</v>
       </c>
       <c r="B14" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2633,48 +2633,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>90569298</v>
+        <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>109815</v>
+        <v>108116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220204</v>
+        <v>219933</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Husås – Andviken – väg Z751, Jmt</t>
+          <t>Mångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488364</v>
+        <v>488418</v>
       </c>
       <c r="R19" t="n">
-        <v>7036217</v>
+        <v>7036250</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,17 +2702,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Allmän</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,23 +2716,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Therese Kalling</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2743,16 +2738,16 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90569298</t>
+          <t>https://artportalen.se/Sighting/136955238</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131359540</v>
+        <v>90569298</v>
       </c>
       <c r="B20" t="n">
-        <v>79350</v>
+        <v>109815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,41 +2755,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>260591</v>
+        <v>220204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Kalvsberget Norra, Jmt</t>
+          <t>Husås – Andviken – väg Z751, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488103</v>
+        <v>488364</v>
       </c>
       <c r="R20" t="n">
-        <v>7036077</v>
+        <v>7036217</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,17 +2809,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Allmän</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,43 +2828,166 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Leif Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emma Karlsson, Therese Kalling</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90569298</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131359540</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>488103</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7036077</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Kristian Zackrisson</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131359540</t>
         </is>
@@ -2903,6 +3014,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
+          <t>Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2084,7 +2084,7 @@
         <v>136532340</v>
       </c>
       <c r="B14" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2084,7 +2084,7 @@
         <v>136532340</v>
       </c>
       <c r="B14" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>136537122</v>
       </c>
       <c r="B16" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>136537147</v>
       </c>
       <c r="B17" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>136537162</v>
       </c>
       <c r="B18" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108154</v>
+        <v>108158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108158</v>
+        <v>108179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108211</v>
+        <v>108213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 3289-2025 artfynd.xlsx
+++ b/artfynd/S 3289-2025 artfynd.xlsx
@@ -2636,7 +2636,7 @@
         <v>136955238</v>
       </c>
       <c r="B19" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
